--- a/analysis/accident-rate/outputs/ระดับจุดเสี่ยง-598คลัสเตอร์-SI+AccidentRate.xlsx
+++ b/analysis/accident-rate/outputs/ระดับจุดเสี่ยง-598คลัสเตอร์-SI+AccidentRate.xlsx
@@ -69117,7 +69117,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>SI = (F + PI) / Total Accident (ณัฐพงศ์ 2558 สมการ 2.6 หน้า 7) · low: SI &lt; 1 · medium: 1 ≤ SI &lt; 2 · high: SI ≥ 2 · จุดตัด ≈ Q3 (0.99) และรั้วบน Q3 + 1.5·IQR (2.05) ของ Tukey (1977) หน้า 39–44 · NIST e-Handbook 7.1.6</t>
+          <t>SI = (F + PI) / Total Accident (ณัฐพงศ์ 2558 สมการ 2.6 หน้า 7) · low: SI &lt; 1 · medium: 1 ≤ SI &lt; 2 · high: SI ≥ 2 · จุดตัด 1 และ 2 กำหนดโดยผู้วิจัย สอดคล้องกับช่วงที่ราบของการกระจาย SI (P76–P83 มีค่า SI = 1.000)</t>
         </is>
       </c>
     </row>
@@ -69168,7 +69168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -69485,61 +69485,57 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>จุดตัด SI 1 และ 2 (Q3 และรั้วบน)</t>
+          <t>รวม Rate กับ Severity (อย่างใดอย่างหนึ่งเกินเกณฑ์)</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tukey, J. W. (1977) Exploratory Data Analysis · NIST/SEMATECH e-Handbook</t>
+          <t>Wisconsin DOT Statewide Average Crash Rates and UCLs</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tukey หน้า 39–44 · NIST หัวข้อ 7.1.6</t>
+          <t>หน้า 9 Figure 3</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>upper inner fence: Q3 + 1.5*IQ … a point beyond an inner fence … is considered a mild outlier</t>
+          <t>Segment Crash Rate &gt; Crash Rate UCL OR KAB Crash Rate &gt; KAB Crash Rate UCL</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
         <is>
-          <t>https://www.itl.nist.gov/div898/handbook/prc/section1/prc16.htm</t>
+          <t>https://wisconsindot.gov/dtsdManuals/traffic-ops/manuals-and-standards/safety/crashrates/rates20.pdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>รวม Rate กับ Severity (อย่างใดอย่างหนึ่งเกินเกณฑ์)</t>
+          <t>ใช้ Severity ร่วมกับวิธีอื่น</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Wisconsin DOT Statewide Average Crash Rates and UCLs</t>
+          <t>ณัฐพงศ์ ซื่อสัตย์ (2558) วิทยานิพนธ์ มทส. การจัดทำแผนที่ความเสี่ยงของทางหลวงในประเทศไทย</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>หน้า 9 Figure 3</t>
+          <t>หน้า 55</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Segment Crash Rate &gt; Crash Rate UCL OR KAB Crash Rate &gt; KAB Crash Rate UCL</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>https://wisconsindot.gov/dtsdManuals/traffic-ops/manuals-and-standards/safety/crashrates/rates20.pdf</t>
-        </is>
-      </c>
+          <t>สามารถใช้วิธี Accident Severity ร่วมกับวิธีการอื่นได้ ในการศึกษาต่อๆไป</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>ใช้ Severity ร่วมกับวิธีอื่น</t>
+          <t>L = 1 กม.</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -69549,38 +69545,15 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>หน้า 55</t>
+          <t>หน้า 35–36 และหน้า 51</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>สามารถใช้วิธี Accident Severity ร่วมกับวิธีการอื่นได้ ในการศึกษาต่อๆไป</t>
+          <t>สำหรับช่วงถนน 1 กิโลเมตร</t>
         </is>
       </c>
       <c r="E15" s="9" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>L = 1 กม.</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>ณัฐพงศ์ ซื่อสัตย์ (2558) วิทยานิพนธ์ มทส. การจัดทำแผนที่ความเสี่ยงของทางหลวงในประเทศไทย</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>หน้า 35–36 และหน้า 51</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>สำหรับช่วงถนน 1 กิโลเมตร</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -69591,7 +69564,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
